--- a/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.4.1 Name Arrays working file.xlsx
+++ b/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.4.1 Name Arrays working file.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="28702"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/travis/Dropbox/Data Handling in Excel/03 Naming Arrays/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rittiv/Documents/GitHub/Projects-Data/1.7. EXCEL  SECTION - Advanced Formulas and Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0E87FE-C77A-0A4F-BCC6-D1CEEB76CEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7700" yWindow="7820" windowWidth="25600" windowHeight="14400"/>
+    <workbookView xWindow="25620" yWindow="620" windowWidth="25600" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marketing_perf" sheetId="6" r:id="rId1"/>
@@ -17,11 +18,23 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">marketing_perf!#REF!</definedName>
+    <definedName name="Marketing">marketing_perf!$A$1:$H$381</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -1251,13 +1264,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1837,7 +1850,7 @@
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1848,35 +1861,35 @@
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="22" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="20" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="20" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="22" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="38" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="38" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1884,8 +1897,8 @@
     <xf numFmtId="0" fontId="20" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="36" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="36" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="1" fillId="36" borderId="0" xfId="48" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -1937,7 +1950,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Percent" xfId="48" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="48" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -1947,6 +1960,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2238,7 +2254,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M381"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2324,15 +2340,15 @@
         <v>64</v>
       </c>
       <c r="K2" s="14" t="str">
-        <f>VLOOKUP(J2,$A$2:$H$381,2,FALSE)</f>
+        <f>VLOOKUP(J2,Marketing,2,FALSE)</f>
         <v>Designer</v>
       </c>
       <c r="L2" s="15">
-        <f>VLOOKUP(J2,$A$2:$H$381,7,FALSE)</f>
+        <f>VLOOKUP(J2,Marketing,7,FALSE)</f>
         <v>250</v>
       </c>
       <c r="M2" s="17">
-        <f>VLOOKUP(J2,$A$2:$H$381,8,FALSE)</f>
+        <f>VLOOKUP(J2,Marketing,8,FALSE)</f>
         <v>13.11</v>
       </c>
     </row>
@@ -2365,15 +2381,15 @@
         <v>60</v>
       </c>
       <c r="K3" s="14" t="str">
-        <f t="shared" ref="K3:K11" si="0">VLOOKUP(J3,$A$2:$H$381,2,FALSE)</f>
+        <f>VLOOKUP(J3,Marketing,2,FALSE)</f>
         <v>None</v>
       </c>
       <c r="L3" s="15">
-        <f t="shared" ref="L3:L11" si="1">VLOOKUP(J3,$A$2:$H$381,7,FALSE)</f>
+        <f>VLOOKUP(J3,Marketing,7,FALSE)</f>
         <v>260</v>
       </c>
       <c r="M3" s="17">
-        <f t="shared" ref="M3:M11" si="2">VLOOKUP(J3,$A$2:$H$381,8,FALSE)</f>
+        <f>VLOOKUP(J3,Marketing,8,FALSE)</f>
         <v>22.6</v>
       </c>
     </row>
@@ -2406,15 +2422,15 @@
         <v>11</v>
       </c>
       <c r="K4" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J4,Marketing,2,FALSE)</f>
         <v>Discount</v>
       </c>
       <c r="L4" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J4,Marketing,7,FALSE)</f>
         <v>966</v>
       </c>
       <c r="M4" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J4,Marketing,8,FALSE)</f>
         <v>465.24</v>
       </c>
     </row>
@@ -2447,15 +2463,15 @@
         <v>15</v>
       </c>
       <c r="K5" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J5,Marketing,2,FALSE)</f>
         <v>None</v>
       </c>
       <c r="L5" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J5,Marketing,7,FALSE)</f>
         <v>720</v>
       </c>
       <c r="M5" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J5,Marketing,8,FALSE)</f>
         <v>11.92</v>
       </c>
     </row>
@@ -2488,15 +2504,15 @@
         <v>20</v>
       </c>
       <c r="K6" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J6,Marketing,2,FALSE)</f>
         <v>Discount</v>
       </c>
       <c r="L6" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J6,Marketing,7,FALSE)</f>
         <v>632</v>
       </c>
       <c r="M6" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J6,Marketing,8,FALSE)</f>
         <v>159.16</v>
       </c>
     </row>
@@ -2529,15 +2545,15 @@
         <v>84</v>
       </c>
       <c r="K7" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J7,Marketing,2,FALSE)</f>
         <v>None</v>
       </c>
       <c r="L7" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J7,Marketing,7,FALSE)</f>
         <v>160.6</v>
       </c>
       <c r="M7" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J7,Marketing,8,FALSE)</f>
         <v>111.2</v>
       </c>
     </row>
@@ -2570,15 +2586,15 @@
         <v>33</v>
       </c>
       <c r="K8" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J8,Marketing,2,FALSE)</f>
         <v>Designer</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J8,Marketing,7,FALSE)</f>
         <v>413</v>
       </c>
       <c r="M8" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J8,Marketing,8,FALSE)</f>
         <v>67</v>
       </c>
     </row>
@@ -2611,15 +2627,15 @@
         <v>63</v>
       </c>
       <c r="K9" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J9,Marketing,2,FALSE)</f>
         <v>Designer</v>
       </c>
       <c r="L9" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J9,Marketing,7,FALSE)</f>
         <v>258</v>
       </c>
       <c r="M9" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J9,Marketing,8,FALSE)</f>
         <v>135.78</v>
       </c>
     </row>
@@ -2652,15 +2668,15 @@
         <v>333</v>
       </c>
       <c r="K10" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J10,Marketing,2,FALSE)</f>
         <v>None</v>
       </c>
       <c r="L10" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J10,Marketing,7,FALSE)</f>
         <v>0</v>
       </c>
       <c r="M10" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J10,Marketing,8,FALSE)</f>
         <v>5.0199999999999996</v>
       </c>
     </row>
@@ -2693,15 +2709,15 @@
         <v>28</v>
       </c>
       <c r="K11" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(J11,Marketing,2,FALSE)</f>
         <v>None</v>
       </c>
       <c r="L11" s="15">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(J11,Marketing,7,FALSE)</f>
         <v>467.83</v>
       </c>
       <c r="M11" s="17">
-        <f t="shared" si="2"/>
+        <f>VLOOKUP(J11,Marketing,8,FALSE)</f>
         <v>295.19</v>
       </c>
     </row>
@@ -12326,7 +12342,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:H383">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H383">
     <sortCondition descending="1" ref="G2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12334,7 +12350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
